--- a/public/brdp-template-3-0-1.xlsx
+++ b/public/brdp-template-3-0-1.xlsx
@@ -620,14 +620,8 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>&lt;objrule id="XML-R-0001"&gt;
-  &lt;objpath objappl="1"&gt;//orig/@origname&lt;/objpath&gt;
+  &lt;objpath objappl="0"&gt;//orig[not(@origname='ESCRIBANO MECHANICAL AND ENGINEERING SL' or @origname='INDRA SISTEMAS SA' or @origname='JEFATURA DEL MANDO DE APOYO LOGISTICO DEL ET' or @origname='SANTA BARBARA SISTEMAS SA' or @origname='TESS-DEFENCE SA' or @origname='SAPA OPERACIONES SL')]&lt;/objpath&gt;
   &lt;objuse&gt;Códigos Origname permitidos.&lt;/objuse&gt;
-  &lt;objval valtype="single" val1="ESCRIBANO MECHANICAL AND ENGINEERING SL"&gt;&lt;/objval&gt;
-  &lt;objval valtype="single" val1="INDRA SISTEMAS SA"&gt;&lt;/objval&gt;
-  &lt;objval valtype="single" val1="JEFATURA DEL MANDO DE APOYO LOGISTICO DEL ET"&gt;&lt;/objval&gt;
-  &lt;objval valtype="single" val1="SANTA BARBARA SISTEMAS SA"&gt;&lt;/objval&gt;
-  &lt;objval valtype="single" val1="TESS-DEFENCE SA"&gt;&lt;/objval&gt;
-  &lt;objval valtype="single" val1="SAPA OPERACIONES SL"&gt;&lt;/objval&gt;
 &lt;/objrule&gt;</t>
         </is>
       </c>
@@ -753,9 +747,8 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>&lt;objrule id="XML-R-2652"&gt;
-  &lt;objpath objappl="1"&gt;//status/qa/firstver/@type&lt;/objpath&gt;
+  &lt;objpath objappl="0"&gt;//status/qa/firstver[not(@type='tabtop')]&lt;/objpath&gt;
   &lt;objuse&gt;Obligatorio el atributo type de firstver y su valor debe ser tabtop&lt;/objuse&gt;
-  &lt;objval val1="tabtop"&gt;&lt;/objval&gt;
 &lt;/objrule&gt;</t>
         </is>
       </c>

--- a/public/brdp-template-3-0-1.xlsx
+++ b/public/brdp-template-3-0-1.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>El atributo "origname" de &lt;orig&gt; debe ser uno de estos 6 valores: "ESCRIBANO MECHANICAL AND ENGINEERING SL", "INDRA SISTEMAS SA", "JEFATURA DEL MANDO DE APOYO LOGISTICO DEL ET", "SANTA BARBARA SISTEMAS SA", "TESS-DEFENCE SA", "SAPA OPERACIONES SL".</t>
+          <t>Todo &lt;orig&gt; debe llevar el atributo @origname, con uno de estos 6 valores: "ESCRIBANO MECHANICAL AND ENGINEERING SL", "INDRA SISTEMAS SA", "JEFATURA DEL MANDO DE APOYO LOGISTICO DEL ET", "SANTA BARBARA SISTEMAS SA", "TESS-DEFENCE SA", "SAPA OPERACIONES SL".</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -619,9 +619,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>&lt;objrule id="XML-R-0001"&gt;
-  &lt;objpath objappl="0"&gt;//orig[not(@origname='ESCRIBANO MECHANICAL AND ENGINEERING SL' or @origname='INDRA SISTEMAS SA' or @origname='JEFATURA DEL MANDO DE APOYO LOGISTICO DEL ET' or @origname='SANTA BARBARA SISTEMAS SA' or @origname='TESS-DEFENCE SA' or @origname='SAPA OPERACIONES SL')]&lt;/objpath&gt;
-  &lt;objuse&gt;Códigos Origname permitidos.&lt;/objuse&gt;
+          <t>&lt;objrule id="XML-R-0001-1"&gt;
+  &lt;objpath&gt;//orig/@origname&lt;/objpath&gt;
+  &lt;objuse&gt;El atributo @origname de &amp;lt;orig&amp;gt; solo puede tomar uno de los 6 valores autorizados.&lt;/objuse&gt;
+  &lt;objval valtype="single" val1="ESCRIBANO MECHANICAL AND ENGINEERING SL"&gt;&lt;/objval&gt;
+  &lt;objval valtype="single" val1="INDRA SISTEMAS SA"&gt;&lt;/objval&gt;
+  &lt;objval valtype="single" val1="JEFATURA DEL MANDO DE APOYO LOGISTICO DEL ET"&gt;&lt;/objval&gt;
+  &lt;objval valtype="single" val1="SANTA BARBARA SISTEMAS SA"&gt;&lt;/objval&gt;
+  &lt;objval valtype="single" val1="TESS-DEFENCE SA"&gt;&lt;/objval&gt;
+  &lt;objval valtype="single" val1="SAPA OPERACIONES SL"&gt;&lt;/objval&gt;
+&lt;/objrule&gt;
+&lt;objrule id="XML-R-0001-2"&gt;
+  &lt;objpath objappl="0"&gt;//orig[not(@origname)]&lt;/objpath&gt;
+  &lt;objuse&gt;Todo &amp;lt;orig&amp;gt; debe llevar el atributo @origname.&lt;/objuse&gt;
 &lt;/objrule&gt;</t>
         </is>
       </c>
